--- a/experiment/ELAN_bestx8/Test/results_table.xlsx
+++ b/experiment/ELAN_bestx8/Test/results_table.xlsx
@@ -565,43 +565,43 @@
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">
-2,505K</t>
+1,460K</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>24.466/
-0.6232</t>
+          <t>27.005/
+0.7691</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>23.247/
-0.5398</t>
+          <t>25.077/
+0.6407</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>23.660/
-0.5216</t>
+          <t>24.848/
+0.5987</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>20.812/
-0.4909</t>
+          <t>22.621/
+0.6207</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>21.580/
-0.6082</t>
+          <t>24.714/
+0.7770</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>22.753/
-0.5567</t>
+          <t>24.853/
+0.6812</t>
         </is>
       </c>
     </row>
